--- a/artfynd/A 28721-2026 artfynd.xlsx
+++ b/artfynd/A 28721-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017283</v>
+        <v>134665054</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674474</v>
+        <v>674349</v>
       </c>
       <c r="R5" t="n">
-        <v>7132818</v>
+        <v>7132733</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1062,12 +1062,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1099,32 +1109,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126017280</v>
+        <v>126017283</v>
       </c>
       <c r="B6" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>674398</v>
+        <v>674474</v>
       </c>
       <c r="R6" t="n">
-        <v>7132786</v>
+        <v>7132818</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1202,6 +1212,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126017280</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vänjaurträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>674398</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7132786</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28721-2026 artfynd.xlsx
+++ b/artfynd/A 28721-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017282</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017279</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665054</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017283</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,8 +1348,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017280</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>